--- a/Telecom_Bill_Dummy_Data_v1.xlsx
+++ b/Telecom_Bill_Dummy_Data_v1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bcld\MSDD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bcld\documentdesigner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABC421A6-D6BC-4196-97F0-8F5FD685472C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D3E866-FAA3-4C92-85F3-D14DDBE81B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="115">
   <si>
     <t>RecordID</t>
   </si>
@@ -350,13 +350,46 @@
   </si>
   <si>
     <t>One Year Price Reserve</t>
+  </si>
+  <si>
+    <t>custmsdn</t>
+  </si>
+  <si>
+    <t>contactno</t>
+  </si>
+  <si>
+    <t>custemail</t>
+  </si>
+  <si>
+    <t>prevbill</t>
+  </si>
+  <si>
+    <t>paymrcvd</t>
+  </si>
+  <si>
+    <t>curbill</t>
+  </si>
+  <si>
+    <t>customer@mail.com</t>
+  </si>
+  <si>
+    <t>curchrgs</t>
+  </si>
+  <si>
+    <t>curtaxes</t>
+  </si>
+  <si>
+    <t>totdue</t>
+  </si>
+  <si>
+    <t>prevbil</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -368,6 +401,20 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -413,10 +460,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -430,8 +478,13 @@
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -732,27 +785,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="27.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="15" width="20.5546875" customWidth="1"/>
+    <col min="16" max="16" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -769,43 +823,73 @@
         <v>51</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -821,44 +905,74 @@
       <c r="E2" t="s">
         <v>62</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2">
+        <v>987654321</v>
+      </c>
+      <c r="G2">
+        <v>9988776655</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I2">
+        <v>1000</v>
+      </c>
+      <c r="J2">
+        <v>1000</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>700</v>
+      </c>
+      <c r="M2">
+        <v>100</v>
+      </c>
+      <c r="N2">
+        <v>800</v>
+      </c>
+      <c r="O2">
+        <v>800</v>
+      </c>
+      <c r="P2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
+      <c r="Q2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" t="s">
+      <c r="R2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="S2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="T2" t="s">
         <v>20</v>
       </c>
-      <c r="K2">
+      <c r="U2">
         <v>300</v>
       </c>
-      <c r="L2">
+      <c r="V2">
         <v>120</v>
       </c>
-      <c r="M2">
+      <c r="W2">
         <v>30</v>
       </c>
-      <c r="N2">
+      <c r="X2">
         <v>45</v>
       </c>
-      <c r="O2">
+      <c r="Y2">
         <v>495</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Z2" t="s">
         <v>21</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="AA2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -874,44 +988,74 @@
       <c r="E3" t="s">
         <v>62</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3">
+        <v>987654321</v>
+      </c>
+      <c r="G3">
+        <v>9988776655</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I3">
+        <v>1000</v>
+      </c>
+      <c r="J3">
+        <v>1000</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>700</v>
+      </c>
+      <c r="M3">
+        <v>100</v>
+      </c>
+      <c r="N3">
+        <v>800</v>
+      </c>
+      <c r="O3">
+        <v>800</v>
+      </c>
+      <c r="P3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" t="s">
+      <c r="Q3" t="s">
         <v>17</v>
       </c>
-      <c r="H3" t="s">
+      <c r="R3" t="s">
         <v>18</v>
       </c>
-      <c r="I3" t="s">
+      <c r="S3" t="s">
         <v>19</v>
       </c>
-      <c r="J3" t="s">
+      <c r="T3" t="s">
         <v>20</v>
       </c>
-      <c r="K3">
+      <c r="U3">
         <v>300</v>
       </c>
-      <c r="L3">
+      <c r="V3">
         <v>185</v>
       </c>
-      <c r="M3">
+      <c r="W3">
         <v>20</v>
       </c>
-      <c r="N3">
+      <c r="X3">
         <v>50.5</v>
       </c>
-      <c r="O3">
+      <c r="Y3">
         <v>555.5</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Z3" t="s">
         <v>21</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="AA3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -927,44 +1071,74 @@
       <c r="E4" t="s">
         <v>63</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4">
+        <v>987654321</v>
+      </c>
+      <c r="G4">
+        <v>9988776655</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I4">
+        <v>1000</v>
+      </c>
+      <c r="J4">
+        <v>1000</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>700</v>
+      </c>
+      <c r="M4">
+        <v>100</v>
+      </c>
+      <c r="N4">
+        <v>800</v>
+      </c>
+      <c r="O4">
+        <v>800</v>
+      </c>
+      <c r="P4" t="s">
         <v>16</v>
       </c>
-      <c r="G4" t="s">
+      <c r="Q4" t="s">
         <v>17</v>
       </c>
-      <c r="H4" t="s">
+      <c r="R4" t="s">
         <v>18</v>
       </c>
-      <c r="I4" t="s">
+      <c r="S4" t="s">
         <v>19</v>
       </c>
-      <c r="J4" t="s">
+      <c r="T4" t="s">
         <v>20</v>
       </c>
-      <c r="K4">
+      <c r="U4">
         <v>300</v>
       </c>
-      <c r="L4">
+      <c r="V4">
         <v>240</v>
       </c>
-      <c r="M4">
+      <c r="W4">
         <v>30</v>
       </c>
-      <c r="N4">
+      <c r="X4">
         <v>57</v>
       </c>
-      <c r="O4">
+      <c r="Y4">
         <v>627</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Z4" t="s">
         <v>21</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="AA4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -980,44 +1154,74 @@
       <c r="E5" t="s">
         <v>63</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5">
+        <v>987654321</v>
+      </c>
+      <c r="G5">
+        <v>9988776655</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I5">
+        <v>1000</v>
+      </c>
+      <c r="J5">
+        <v>1000</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>700</v>
+      </c>
+      <c r="M5">
+        <v>100</v>
+      </c>
+      <c r="N5">
+        <v>800</v>
+      </c>
+      <c r="O5">
+        <v>800</v>
+      </c>
+      <c r="P5" t="s">
         <v>16</v>
       </c>
-      <c r="G5" t="s">
+      <c r="Q5" t="s">
         <v>17</v>
       </c>
-      <c r="H5" t="s">
+      <c r="R5" t="s">
         <v>18</v>
       </c>
-      <c r="I5" t="s">
+      <c r="S5" t="s">
         <v>19</v>
       </c>
-      <c r="J5" t="s">
+      <c r="T5" t="s">
         <v>20</v>
       </c>
-      <c r="K5">
+      <c r="U5">
         <v>300</v>
       </c>
-      <c r="L5">
+      <c r="V5">
         <v>310</v>
       </c>
-      <c r="M5">
+      <c r="W5">
         <v>20</v>
       </c>
-      <c r="N5">
+      <c r="X5">
         <v>63</v>
       </c>
-      <c r="O5">
+      <c r="Y5">
         <v>693</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Z5" t="s">
         <v>21</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="AA5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -1033,44 +1237,74 @@
       <c r="E6" t="s">
         <v>63</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6">
+        <v>987654321</v>
+      </c>
+      <c r="G6">
+        <v>9988776655</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I6">
+        <v>1000</v>
+      </c>
+      <c r="J6">
+        <v>1000</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>700</v>
+      </c>
+      <c r="M6">
+        <v>100</v>
+      </c>
+      <c r="N6">
+        <v>800</v>
+      </c>
+      <c r="O6">
+        <v>800</v>
+      </c>
+      <c r="P6" t="s">
         <v>16</v>
       </c>
-      <c r="G6" t="s">
+      <c r="Q6" t="s">
         <v>17</v>
       </c>
-      <c r="H6" t="s">
+      <c r="R6" t="s">
         <v>18</v>
       </c>
-      <c r="I6" t="s">
+      <c r="S6" t="s">
         <v>19</v>
       </c>
-      <c r="J6" t="s">
+      <c r="T6" t="s">
         <v>20</v>
       </c>
-      <c r="K6">
+      <c r="U6">
         <v>300</v>
       </c>
-      <c r="L6">
+      <c r="V6">
         <v>275</v>
       </c>
-      <c r="M6">
+      <c r="W6">
         <v>30</v>
       </c>
-      <c r="N6">
+      <c r="X6">
         <v>60.5</v>
       </c>
-      <c r="O6">
+      <c r="Y6">
         <v>665.5</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Z6" t="s">
         <v>21</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="AA6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -1086,44 +1320,74 @@
       <c r="E7" t="s">
         <v>62</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7">
+        <v>987654321</v>
+      </c>
+      <c r="G7">
+        <v>9988776655</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I7">
+        <v>1000</v>
+      </c>
+      <c r="J7">
+        <v>1000</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>700</v>
+      </c>
+      <c r="M7">
+        <v>100</v>
+      </c>
+      <c r="N7">
+        <v>800</v>
+      </c>
+      <c r="O7">
+        <v>800</v>
+      </c>
+      <c r="P7" t="s">
         <v>16</v>
       </c>
-      <c r="G7" t="s">
+      <c r="Q7" t="s">
         <v>17</v>
       </c>
-      <c r="H7" t="s">
+      <c r="R7" t="s">
         <v>18</v>
       </c>
-      <c r="I7" t="s">
+      <c r="S7" t="s">
         <v>19</v>
       </c>
-      <c r="J7" t="s">
+      <c r="T7" t="s">
         <v>20</v>
       </c>
-      <c r="K7">
+      <c r="U7">
         <v>300</v>
       </c>
-      <c r="L7">
+      <c r="V7">
         <v>420</v>
       </c>
-      <c r="M7">
+      <c r="W7">
         <v>20</v>
       </c>
-      <c r="N7">
+      <c r="X7">
         <v>74</v>
       </c>
-      <c r="O7">
+      <c r="Y7">
         <v>814</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Z7" t="s">
         <v>21</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="AA7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -1139,44 +1403,74 @@
       <c r="E8" t="s">
         <v>64</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8">
+        <v>987654321</v>
+      </c>
+      <c r="G8">
+        <v>9988776655</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I8">
+        <v>1000</v>
+      </c>
+      <c r="J8">
+        <v>1000</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>700</v>
+      </c>
+      <c r="M8">
+        <v>100</v>
+      </c>
+      <c r="N8">
+        <v>800</v>
+      </c>
+      <c r="O8">
+        <v>800</v>
+      </c>
+      <c r="P8" t="s">
         <v>16</v>
       </c>
-      <c r="G8" t="s">
+      <c r="Q8" t="s">
         <v>17</v>
       </c>
-      <c r="H8" t="s">
+      <c r="R8" t="s">
         <v>18</v>
       </c>
-      <c r="I8" t="s">
+      <c r="S8" t="s">
         <v>19</v>
       </c>
-      <c r="J8" t="s">
+      <c r="T8" t="s">
         <v>20</v>
       </c>
-      <c r="K8">
+      <c r="U8">
         <v>300</v>
       </c>
-      <c r="L8">
+      <c r="V8">
         <v>360</v>
       </c>
-      <c r="M8">
+      <c r="W8">
         <v>30</v>
       </c>
-      <c r="N8">
+      <c r="X8">
         <v>69</v>
       </c>
-      <c r="O8">
+      <c r="Y8">
         <v>759</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Z8" t="s">
         <v>21</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="AA8" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -1192,44 +1486,74 @@
       <c r="E9" t="s">
         <v>64</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9">
+        <v>987654321</v>
+      </c>
+      <c r="G9">
+        <v>9988776655</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I9">
+        <v>1000</v>
+      </c>
+      <c r="J9">
+        <v>1000</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>700</v>
+      </c>
+      <c r="M9">
+        <v>100</v>
+      </c>
+      <c r="N9">
+        <v>800</v>
+      </c>
+      <c r="O9">
+        <v>800</v>
+      </c>
+      <c r="P9" t="s">
         <v>16</v>
       </c>
-      <c r="G9" t="s">
+      <c r="Q9" t="s">
         <v>17</v>
       </c>
-      <c r="H9" t="s">
+      <c r="R9" t="s">
         <v>18</v>
       </c>
-      <c r="I9" t="s">
+      <c r="S9" t="s">
         <v>19</v>
       </c>
-      <c r="J9" t="s">
+      <c r="T9" t="s">
         <v>20</v>
       </c>
-      <c r="K9">
+      <c r="U9">
         <v>300</v>
       </c>
-      <c r="L9">
+      <c r="V9">
         <v>510</v>
       </c>
-      <c r="M9">
+      <c r="W9">
         <v>20</v>
       </c>
-      <c r="N9">
+      <c r="X9">
         <v>83</v>
       </c>
-      <c r="O9">
+      <c r="Y9">
         <v>913</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Z9" t="s">
         <v>21</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="AA9" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -1245,44 +1569,74 @@
       <c r="E10" t="s">
         <v>64</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10">
+        <v>987654321</v>
+      </c>
+      <c r="G10">
+        <v>9988776655</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I10">
+        <v>1000</v>
+      </c>
+      <c r="J10">
+        <v>1000</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>700</v>
+      </c>
+      <c r="M10">
+        <v>100</v>
+      </c>
+      <c r="N10">
+        <v>800</v>
+      </c>
+      <c r="O10">
+        <v>800</v>
+      </c>
+      <c r="P10" t="s">
         <v>16</v>
       </c>
-      <c r="G10" t="s">
+      <c r="Q10" t="s">
         <v>17</v>
       </c>
-      <c r="H10" t="s">
+      <c r="R10" t="s">
         <v>18</v>
       </c>
-      <c r="I10" t="s">
+      <c r="S10" t="s">
         <v>19</v>
       </c>
-      <c r="J10" t="s">
+      <c r="T10" t="s">
         <v>20</v>
       </c>
-      <c r="K10">
+      <c r="U10">
         <v>300</v>
       </c>
-      <c r="L10">
+      <c r="V10">
         <v>450</v>
       </c>
-      <c r="M10">
+      <c r="W10">
         <v>30</v>
       </c>
-      <c r="N10">
+      <c r="X10">
         <v>78</v>
       </c>
-      <c r="O10">
+      <c r="Y10">
         <v>858</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Z10" t="s">
         <v>21</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="AA10" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -1298,44 +1652,86 @@
       <c r="E11" t="s">
         <v>62</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11">
+        <v>987654321</v>
+      </c>
+      <c r="G11">
+        <v>9988776655</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I11">
+        <v>1000</v>
+      </c>
+      <c r="J11">
+        <v>1000</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>700</v>
+      </c>
+      <c r="M11">
+        <v>100</v>
+      </c>
+      <c r="N11">
+        <v>800</v>
+      </c>
+      <c r="O11">
+        <v>800</v>
+      </c>
+      <c r="P11" t="s">
         <v>16</v>
       </c>
-      <c r="G11" t="s">
+      <c r="Q11" t="s">
         <v>17</v>
       </c>
-      <c r="H11" t="s">
+      <c r="R11" t="s">
         <v>18</v>
       </c>
-      <c r="I11" t="s">
+      <c r="S11" t="s">
         <v>19</v>
       </c>
-      <c r="J11" t="s">
+      <c r="T11" t="s">
         <v>20</v>
       </c>
-      <c r="K11">
+      <c r="U11">
         <v>300</v>
       </c>
-      <c r="L11">
+      <c r="V11">
         <v>600</v>
       </c>
-      <c r="M11">
+      <c r="W11">
         <v>20</v>
       </c>
-      <c r="N11">
+      <c r="X11">
         <v>92</v>
       </c>
-      <c r="O11">
+      <c r="Y11">
         <v>1012</v>
       </c>
-      <c r="P11" t="s">
+      <c r="Z11" t="s">
         <v>21</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="AA11" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{FB24E70A-EA6E-4361-AB82-420D362342BD}"/>
+    <hyperlink ref="H3" r:id="rId2" xr:uid="{418FCCC1-F4B1-460D-B4FE-FCA0EF804E8C}"/>
+    <hyperlink ref="H4" r:id="rId3" xr:uid="{40B98338-AA2D-4893-9323-7F8B772AEB92}"/>
+    <hyperlink ref="H5" r:id="rId4" xr:uid="{E42CBB46-4892-43F4-BD46-47567C76F368}"/>
+    <hyperlink ref="H6" r:id="rId5" xr:uid="{54FB441A-87F9-400B-8751-83C8804E7BE2}"/>
+    <hyperlink ref="H7" r:id="rId6" xr:uid="{2CA40F5A-1317-4A96-9C9B-EC55BB93A7BD}"/>
+    <hyperlink ref="H8" r:id="rId7" xr:uid="{41DB53C3-EE6F-4849-A1F9-2785774CE3D5}"/>
+    <hyperlink ref="H9" r:id="rId8" xr:uid="{A9D5F433-93EA-45A5-8945-A99DCFBC0034}"/>
+    <hyperlink ref="H10" r:id="rId9" xr:uid="{7EB9AE77-483E-4C38-B175-CB641A3417DF}"/>
+    <hyperlink ref="H11" r:id="rId10" xr:uid="{FD77178B-3247-4DE8-9F61-D823FE676603}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
